--- a/Data/Export/Common/Flag_旗帜.xlsx
+++ b/Data/Export/Common/Flag_旗帜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\sango_infinity\Data\Export\Common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E177A9B-F92D-4C6E-BA94-491B02C08AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BD8BC5-CB69-450A-AFFB-A531788F88B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3690" yWindow="2595" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flags" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="185">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -539,6 +539,87 @@
   </si>
   <si>
     <t>164,131,135</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>131,75,59</t>
+  </si>
+  <si>
+    <t>105,236,34</t>
+  </si>
+  <si>
+    <t>37,84,150</t>
+  </si>
+  <si>
+    <t>29,80,200</t>
+  </si>
+  <si>
+    <t>22,171,232</t>
+  </si>
+  <si>
+    <t>10,101,110</t>
+  </si>
+  <si>
+    <t>250,19,86</t>
+  </si>
+  <si>
+    <t>37,242,97</t>
+  </si>
+  <si>
+    <t>132,109,234</t>
+  </si>
+  <si>
+    <t>7,10,30</t>
+  </si>
+  <si>
+    <t>148,123,175</t>
+  </si>
+  <si>
+    <t>45,153,118</t>
+  </si>
+  <si>
+    <t>103,34,230</t>
+  </si>
+  <si>
+    <t>200,138,78</t>
   </si>
 </sst>
 </file>
@@ -1024,23 +1105,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:U68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="3" width="9" style="2"/>
-    <col min="4" max="4" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="71.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="71.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="11" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="12"/>
       <c r="B1" s="9" t="s">
         <v>0</v>
@@ -1067,7 +1148,7 @@
       <c r="T1" s="9"/>
       <c r="U1" s="7"/>
     </row>
-    <row r="2" spans="1:21" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1092,7 +1173,7 @@
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
     </row>
-    <row r="3" spans="1:21" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1123,7 +1204,7 @@
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
     </row>
-    <row r="4" spans="1:21" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -1142,7 +1223,7 @@
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1169,7 +1250,7 @@
       <c r="R5" s="4"/>
       <c r="T5" s="4"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
         <v>8</v>
@@ -1197,7 +1278,7 @@
       <c r="R6" s="4"/>
       <c r="T6" s="4"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
@@ -1224,7 +1305,7 @@
       <c r="R7" s="4"/>
       <c r="T7" s="4"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1251,7 +1332,7 @@
       <c r="R8" s="4"/>
       <c r="T8" s="4"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
@@ -1278,7 +1359,7 @@
       <c r="R9" s="4"/>
       <c r="T9" s="4"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
@@ -1305,7 +1386,7 @@
       <c r="R10" s="4"/>
       <c r="T10" s="4"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
@@ -1332,7 +1413,7 @@
       <c r="R11" s="4"/>
       <c r="T11" s="4"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
@@ -1359,7 +1440,7 @@
       <c r="R12" s="4"/>
       <c r="T12" s="4"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
@@ -1386,7 +1467,7 @@
       <c r="R13" s="4"/>
       <c r="T13" s="4"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
@@ -1413,7 +1494,7 @@
       <c r="R14" s="4"/>
       <c r="T14" s="4"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
@@ -1440,7 +1521,7 @@
       <c r="R15" s="4"/>
       <c r="T15" s="4"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
@@ -1467,7 +1548,7 @@
       <c r="R16" s="4"/>
       <c r="T16" s="4"/>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
@@ -1494,7 +1575,7 @@
       <c r="R17" s="4"/>
       <c r="T17" s="4"/>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B18" s="2" t="s">
         <v>20</v>
       </c>
@@ -1521,7 +1602,7 @@
       <c r="R18" s="4"/>
       <c r="T18" s="4"/>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
@@ -1548,7 +1629,7 @@
       <c r="R19" s="4"/>
       <c r="T19" s="4"/>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
@@ -1575,7 +1656,7 @@
       <c r="R20" s="4"/>
       <c r="T20" s="4"/>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>23</v>
       </c>
@@ -1602,7 +1683,7 @@
       <c r="R21" s="4"/>
       <c r="T21" s="4"/>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>24</v>
       </c>
@@ -1629,7 +1710,7 @@
       <c r="R22" s="4"/>
       <c r="T22" s="4"/>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B23" s="2" t="s">
         <v>25</v>
       </c>
@@ -1656,7 +1737,7 @@
       <c r="R23" s="4"/>
       <c r="T23" s="4"/>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B24" s="2" t="s">
         <v>26</v>
       </c>
@@ -1683,7 +1764,7 @@
       <c r="R24" s="4"/>
       <c r="T24" s="4"/>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B25" s="2" t="s">
         <v>27</v>
       </c>
@@ -1698,7 +1779,7 @@
       </c>
       <c r="F25" s="2" t="str">
         <f ca="1">_xlfn.FLOOR.MATH(RAND()*255)&amp;","&amp;_xlfn.FLOOR.MATH(RAND()*255)&amp;","&amp;_xlfn.FLOOR.MATH(RAND()*255)</f>
-        <v>18,180,163</v>
+        <v>225,236,240</v>
       </c>
       <c r="I25" s="6"/>
       <c r="J25" s="4"/>
@@ -1711,7 +1792,7 @@
       <c r="R25" s="4"/>
       <c r="T25" s="4"/>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B26" s="2" t="s">
         <v>28</v>
       </c>
@@ -1725,8 +1806,8 @@
         <v>92</v>
       </c>
       <c r="F26" s="2" t="str">
-        <f t="shared" ref="F26:F46" ca="1" si="0">_xlfn.FLOOR.MATH(RAND()*255)&amp;","&amp;_xlfn.FLOOR.MATH(RAND()*255)&amp;","&amp;_xlfn.FLOOR.MATH(RAND()*255)</f>
-        <v>34,137,145</v>
+        <f t="shared" ref="F26:F59" ca="1" si="0">_xlfn.FLOOR.MATH(RAND()*255)&amp;","&amp;_xlfn.FLOOR.MATH(RAND()*255)&amp;","&amp;_xlfn.FLOOR.MATH(RAND()*255)</f>
+        <v>113,190,49</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="4"/>
@@ -1739,7 +1820,7 @@
       <c r="R26" s="4"/>
       <c r="T26" s="4"/>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B27" s="2" t="s">
         <v>29</v>
       </c>
@@ -1754,7 +1835,7 @@
       </c>
       <c r="F27" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>62,172,243</v>
+        <v>211,200,84</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="4"/>
@@ -1767,7 +1848,7 @@
       <c r="R27" s="4"/>
       <c r="T27" s="4"/>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B28" s="2" t="s">
         <v>30</v>
       </c>
@@ -1782,7 +1863,7 @@
       </c>
       <c r="F28" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>205,183,126</v>
+        <v>140,32,244</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="4"/>
@@ -1795,7 +1876,7 @@
       <c r="R28" s="4"/>
       <c r="T28" s="4"/>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B29" s="2" t="s">
         <v>31</v>
       </c>
@@ -1810,7 +1891,7 @@
       </c>
       <c r="F29" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>104,242,253</v>
+        <v>80,241,122</v>
       </c>
       <c r="I29" s="6"/>
       <c r="J29" s="4"/>
@@ -1823,7 +1904,7 @@
       <c r="R29" s="4"/>
       <c r="T29" s="4"/>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>32</v>
       </c>
@@ -1838,7 +1919,7 @@
       </c>
       <c r="F30" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30,105,225</v>
+        <v>44,218,194</v>
       </c>
       <c r="I30" s="6"/>
       <c r="J30" s="4"/>
@@ -1851,7 +1932,7 @@
       <c r="R30" s="4"/>
       <c r="T30" s="4"/>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B31" s="2" t="s">
         <v>33</v>
       </c>
@@ -1866,7 +1947,7 @@
       </c>
       <c r="F31" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>218,197,141</v>
+        <v>83,217,243</v>
       </c>
       <c r="I31" s="6"/>
       <c r="J31" s="4"/>
@@ -1879,7 +1960,7 @@
       <c r="R31" s="4"/>
       <c r="T31" s="4"/>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B32" s="2" t="s">
         <v>34</v>
       </c>
@@ -1894,7 +1975,7 @@
       </c>
       <c r="F32" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>199,91,35</v>
+        <v>107,106,27</v>
       </c>
       <c r="I32" s="6"/>
       <c r="J32" s="4"/>
@@ -1907,7 +1988,7 @@
       <c r="R32" s="4"/>
       <c r="T32" s="4"/>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B33" s="2" t="s">
         <v>35</v>
       </c>
@@ -1922,7 +2003,7 @@
       </c>
       <c r="F33" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>54,8,150</v>
+        <v>132,223,186</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="4"/>
@@ -1935,7 +2016,7 @@
       <c r="R33" s="4"/>
       <c r="T33" s="4"/>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B34" s="2" t="s">
         <v>36</v>
       </c>
@@ -1950,7 +2031,7 @@
       </c>
       <c r="F34" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>224,16,190</v>
+        <v>166,50,61</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="4"/>
@@ -1963,7 +2044,7 @@
       <c r="R34" s="4"/>
       <c r="T34" s="4"/>
     </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B35" s="2" t="s">
         <v>37</v>
       </c>
@@ -1978,7 +2059,7 @@
       </c>
       <c r="F35" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>78,116,10</v>
+        <v>29,37,228</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="4"/>
@@ -1991,7 +2072,7 @@
       <c r="R35" s="4"/>
       <c r="T35" s="4"/>
     </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B36" s="2" t="s">
         <v>38</v>
       </c>
@@ -2006,7 +2087,7 @@
       </c>
       <c r="F36" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>1,91,139</v>
+        <v>35,157,185</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="4"/>
@@ -2019,7 +2100,7 @@
       <c r="R36" s="4"/>
       <c r="T36" s="4"/>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B37" s="2" t="s">
         <v>39</v>
       </c>
@@ -2034,7 +2115,7 @@
       </c>
       <c r="F37" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>252,180,116</v>
+        <v>239,83,7</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
@@ -2046,7 +2127,7 @@
       <c r="R37" s="4"/>
       <c r="T37" s="4"/>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B38" s="2" t="s">
         <v>40</v>
       </c>
@@ -2061,7 +2142,7 @@
       </c>
       <c r="F38" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>208,91,26</v>
+        <v>73,245,143</v>
       </c>
       <c r="I38" s="6"/>
       <c r="J38" s="4"/>
@@ -2074,7 +2155,7 @@
       <c r="R38" s="4"/>
       <c r="T38" s="4"/>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>41</v>
       </c>
@@ -2089,7 +2170,7 @@
       </c>
       <c r="F39" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>7,96,184</v>
+        <v>92,159,21</v>
       </c>
       <c r="I39" s="6"/>
       <c r="J39" s="4"/>
@@ -2102,7 +2183,7 @@
       <c r="R39" s="4"/>
       <c r="T39" s="4"/>
     </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B40" s="2" t="s">
         <v>42</v>
       </c>
@@ -2117,7 +2198,7 @@
       </c>
       <c r="F40" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>204,193,107</v>
+        <v>111,51,19</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="4"/>
@@ -2130,7 +2211,7 @@
       <c r="R40" s="4"/>
       <c r="T40" s="4"/>
     </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B41" s="2" t="s">
         <v>43</v>
       </c>
@@ -2145,7 +2226,7 @@
       </c>
       <c r="F41" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>126,75,35</v>
+        <v>71,134,144</v>
       </c>
       <c r="I41" s="6"/>
       <c r="J41" s="4"/>
@@ -2158,7 +2239,7 @@
       <c r="R41" s="4"/>
       <c r="T41" s="4"/>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B42" s="2" t="s">
         <v>44</v>
       </c>
@@ -2173,7 +2254,7 @@
       </c>
       <c r="F42" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>182,122,48</v>
+        <v>253,152,34</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="4"/>
@@ -2186,7 +2267,7 @@
       <c r="R42" s="4"/>
       <c r="T42" s="4"/>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B43" s="2" t="s">
         <v>45</v>
       </c>
@@ -2201,7 +2282,7 @@
       </c>
       <c r="F43" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>197,19,185</v>
+        <v>60,45,167</v>
       </c>
       <c r="I43" s="6"/>
       <c r="J43" s="4"/>
@@ -2214,7 +2295,7 @@
       <c r="R43" s="4"/>
       <c r="T43" s="4"/>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B44" s="2" t="s">
         <v>46</v>
       </c>
@@ -2229,7 +2310,7 @@
       </c>
       <c r="F44" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>52,237,115</v>
+        <v>242,176,146</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="4"/>
@@ -2242,7 +2323,7 @@
       <c r="R44" s="4"/>
       <c r="T44" s="4"/>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B45" s="2" t="s">
         <v>47</v>
       </c>
@@ -2257,7 +2338,7 @@
       </c>
       <c r="F45" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>4,29,163</v>
+        <v>239,95,235</v>
       </c>
       <c r="I45" s="6"/>
       <c r="J45" s="4"/>
@@ -2270,7 +2351,7 @@
       <c r="R45" s="4"/>
       <c r="T45" s="4"/>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B46" s="2" t="s">
         <v>48</v>
       </c>
@@ -2281,11 +2362,11 @@
         <v>112</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="F46" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>111,238,210</v>
+        <v>151,38,47</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="4"/>
@@ -2297,133 +2378,341 @@
       <c r="R46" s="4"/>
       <c r="T46" s="4"/>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.15">
+      <c r="B47" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>187,199,248</v>
+      </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.15">
+      <c r="B48" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F48" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>100,236,157</v>
+      </c>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
     </row>
-    <row r="49" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B49" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F49" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>173,194,244</v>
+      </c>
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
     </row>
-    <row r="50" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B50" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F50" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>101,51,129</v>
+      </c>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
     </row>
-    <row r="51" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B51" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F51" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>123,40,94</v>
+      </c>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
     </row>
-    <row r="52" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B52" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F52" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>13,117,108</v>
+      </c>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
     </row>
-    <row r="53" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B53" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F53" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>0,181,127</v>
+      </c>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
     </row>
-    <row r="54" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B54" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F54" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>204,56,225</v>
+      </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
     </row>
-    <row r="55" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B55" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F55" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>135,231,73</v>
+      </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
     </row>
-    <row r="56" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B56" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F56" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>154,34,51</v>
+      </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
     </row>
-    <row r="57" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B57" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F57" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>224,180,134</v>
+      </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
     </row>
-    <row r="58" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B58" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F58" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>188,144,48</v>
+      </c>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
     </row>
-    <row r="59" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B59" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F59" s="2" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>248,228,190</v>
+      </c>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
     </row>
-    <row r="60" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
     </row>
-    <row r="61" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.15">
       <c r="J61" s="4"/>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
     </row>
-    <row r="62" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.15">
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
     </row>
-    <row r="63" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.15">
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
     </row>
-    <row r="64" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.15">
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
     </row>
-    <row r="65" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="10:13" x14ac:dyDescent="0.15">
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
     </row>
-    <row r="66" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="10:13" x14ac:dyDescent="0.15">
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
     </row>
-    <row r="67" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="10:13" x14ac:dyDescent="0.15">
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
     </row>
-    <row r="68" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="10:13" x14ac:dyDescent="0.15">
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
